--- a/test/fixtures/xlsx/record-trim/record-trim.xlsx
+++ b/test/fixtures/xlsx/record-trim/record-trim.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="56">
   <si>
     <t xml:space="preserve">~~table:Loot~~</t>
   </si>
@@ -159,6 +159,9 @@
   </si>
   <si>
     <t xml:space="preserve">two</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
   </si>
   <si>
     <t xml:space="preserve">gap</t>
@@ -560,13 +563,13 @@
         <v>39</v>
       </c>
       <c r="J10" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="K10" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="L10" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="M10" t="s">
         <v>43</v>
@@ -589,7 +592,7 @@
         <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
         <v>35</v>
@@ -601,13 +604,13 @@
         <v>36</v>
       </c>
       <c r="G11" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="H11" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="I11" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="J11" t="s">
         <v>40</v>
@@ -636,43 +639,43 @@
     </row>
     <row r="12">
       <c r="B12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="G12" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="H12" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="I12" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="J12" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="K12" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="L12" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="M12" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="N12" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="O12" t="s">
         <v>45</v>
@@ -689,7 +692,7 @@
         <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
         <v>35</v>
@@ -701,34 +704,34 @@
         <v>36</v>
       </c>
       <c r="G13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I13" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="J13" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="K13" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="L13" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="M13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O13" t="s">
         <v>45</v>
       </c>
       <c r="P13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q13" t="s">
         <v>5</v>
